--- a/questionnaire_templates/008_digital_inclusion_among_low_income_groups_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/008_digital_inclusion_among_low_income_groups_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -642,8 +642,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -671,12 +671,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'smartphone',_'value':_'smartphone'}</t>
+          <t>smartphone</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'smartphone', 'value': 'smartphone'}</t>
+          <t>smartphone</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'desktop_computer',_'value':_'desktop_computer'}</t>
+          <t>desktop_computer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'desktop_computer', 'value': 'desktop_computer'}</t>
+          <t>desktop computer</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'laptop',_'value':_'laptop'}</t>
+          <t>laptop</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'laptop', 'value': 'laptop'}</t>
+          <t>laptop</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'tablet',_'value':_'tablet'}</t>
+          <t>tablet</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'tablet', 'value': 'tablet'}</t>
+          <t>tablet</t>
         </is>
       </c>
     </row>
@@ -739,12 +739,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'smart_tv',_'value':_'smart_tv'}</t>
+          <t>smart_tv</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'smart_tv', 'value': 'smart_tv'}</t>
+          <t>smart tv</t>
         </is>
       </c>
     </row>
@@ -756,12 +756,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'gaming_console',_'value':_'gaming_console'}</t>
+          <t>gaming_console</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'gaming_console', 'value': 'gaming_console'}</t>
+          <t>gaming console</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'other', 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -790,12 +790,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'none', 'value': 'none'}</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'lack_of_device_access',_'value':_'lack_of_device_access'}</t>
+          <t>lack_of_device_access</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'lack_of_device_access', 'value': 'lack_of_device_access'}</t>
+          <t>lack of device access</t>
         </is>
       </c>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'lack_of_internet_access',_'value':_'lack_of_internet_access'}</t>
+          <t>lack_of_internet_access</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'lack_of_internet_access', 'value': 'lack_of_internet_access'}</t>
+          <t>lack of internet access</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'lack_of_affordability',_'value':_'lack_of_affordability'}</t>
+          <t>lack_of_affordability</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'lack_of_affordability', 'value': 'lack_of_affordability'}</t>
+          <t>lack of affordability</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'lack_of_literacy',_'value':_'lack_of_literacy'}</t>
+          <t>lack_of_literacy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'lack_of_literacy', 'value': 'lack_of_literacy'}</t>
+          <t>lack of literacy</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'lack_of_trust',_'value':_'lack_of_trust'}</t>
+          <t>lack_of_trust</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'lack_of_trust', 'value': 'lack_of_trust'}</t>
+          <t>lack of trust</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'other', 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'none', 'value': 'none'}</t>
+          <t>none</t>
         </is>
       </c>
     </row>
